--- a/output/pdf_financials_xlsx/PWR.xlsx
+++ b/output/pdf_financials_xlsx/PWR.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.352207</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.331482</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.506903</v>
       </c>
     </row>
     <row r="93">
@@ -3170,7 +3170,11 @@
           <t>Warrants reserves 10</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3608,7 +3612,11 @@
           <t>Warrants reserves 9</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>5.352207</v>
       </c>

--- a/output/pdf_financials_xlsx/PWR.xlsx
+++ b/output/pdf_financials_xlsx/PWR.xlsx
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005444</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010334</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002247</v>
       </c>
     </row>
     <row r="35">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005444</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010334</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002247</v>
       </c>
     </row>
     <row r="37">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.700698</v>
+        <v>2.690364</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.119052</v>
+        <v>0.116805</v>
       </c>
     </row>
     <row r="49">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">

--- a/output/pdf_financials_xlsx/PWR.xlsx
+++ b/output/pdf_financials_xlsx/PWR.xlsx
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-6.08511</v>
+        <v>-6.143098</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-1.037464</v>
+        <v>-0.586604</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-1.037464</v>
+        <v>-0.932075</v>
       </c>
     </row>
     <row r="21">
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.5314759999999999</v>
       </c>
     </row>
     <row r="108">
@@ -3897,7 +3897,11 @@
           <t>Share-based compensation expense 10</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -4207,7 +4211,11 @@
           <t>Proceeds from private placement 10</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -4866,7 +4874,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>3.28</v>
       </c>
@@ -5478,7 +5490,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>-6.143098</v>
       </c>
